--- a/Assignments/Excel_Text_Date_Functions - assignment.xlsx
+++ b/Assignments/Excel_Text_Date_Functions - assignment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/17452af9f4891f04/Desktop/Excel New/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4f5269e412419e72/Documents/Excel ITvedant/Assignments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="13_ncr:1_{43AF9261-C66E-40DE-80A3-C3F14857886D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC105BC6-A1A1-4A39-A2F2-432857640629}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="13_ncr:1_{43AF9261-C66E-40DE-80A3-C3F14857886D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4172B976-2F61-4ED8-BF36-AE4F1DDE6B3F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CRM Dataset" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,24 @@
     <sheet name="Practice Exercises" sheetId="10" r:id="rId10"/>
     <sheet name="Quick Reference" sheetId="11" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <definedNames>
+    <definedName name="city">'CRM Dataset'!$E$4:$E$28</definedName>
+    <definedName name="cust_email">'CRM Dataset'!$C$4:$C$28</definedName>
+    <definedName name="cust_name">'CRM Dataset'!$B$4:$B$28</definedName>
+    <definedName name="cust_phone">'CRM Dataset'!$D$4:$D$28</definedName>
+    <definedName name="CustID">'CRM Dataset'!$A$4:$A$28</definedName>
+    <definedName name="join_date">'CRM Dataset'!$K$4:$K$28</definedName>
+    <definedName name="last_login_time">'CRM Dataset'!$O$4:$O$28</definedName>
+    <definedName name="last_name">'CRM Dataset'!$L$4:$L$28</definedName>
+    <definedName name="plan">'CRM Dataset'!$H$4:$H$28</definedName>
+    <definedName name="region">'CRM Dataset'!$F$4:$F$28</definedName>
+    <definedName name="Renewal_Date">'CRM Dataset'!$M$4:$M$28</definedName>
+    <definedName name="revenue">'CRM Dataset'!$N$4:$N$28</definedName>
+    <definedName name="segment">'CRM Dataset'!$G$4:$G$28</definedName>
+    <definedName name="source">'CRM Dataset'!$J$4:$J$28</definedName>
+    <definedName name="Status">'CRM Dataset'!$I$4:$I$28</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,6 +52,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -2798,7 +2818,7 @@
     <numFmt numFmtId="165" formatCode="mm/dd/yy"/>
     <numFmt numFmtId="166" formatCode="mm/dd/yy\ hh:mm\ AM/PM"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2811,100 +2831,100 @@
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF1A5276"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF4A4A4A"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF7D6608"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2918,6 +2938,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -4012,25 +4033,25 @@
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:O28"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="14" width="11" customWidth="1"/>
-    <col min="15" max="15" width="20" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="37.5" customHeight="1">
+    <row r="1" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="141" t="s">
         <v>0</v>
       </c>
@@ -4049,7 +4070,7 @@
       <c r="N1" s="141"/>
       <c r="O1" s="141"/>
     </row>
-    <row r="2" spans="1:15" ht="30" customHeight="1">
+    <row r="2" spans="1:15" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="142" t="s">
         <v>1</v>
       </c>
@@ -4068,7 +4089,7 @@
       <c r="N2" s="142"/>
       <c r="O2" s="142"/>
     </row>
-    <row r="3" spans="1:15" ht="21.75" customHeight="1">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -4115,7 +4136,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.75" customHeight="1">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -4162,7 +4183,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.75" customHeight="1">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>28</v>
       </c>
@@ -4209,7 +4230,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.75" customHeight="1">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
@@ -4256,7 +4277,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.75" customHeight="1">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>45</v>
       </c>
@@ -4303,7 +4324,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.75" customHeight="1">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>54</v>
       </c>
@@ -4350,7 +4371,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
@@ -4397,7 +4418,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>70</v>
       </c>
@@ -4444,7 +4465,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>79</v>
       </c>
@@ -4491,7 +4512,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.75" customHeight="1">
+    <row r="12" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>85</v>
       </c>
@@ -4538,7 +4559,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>92</v>
       </c>
@@ -4585,7 +4606,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>97</v>
       </c>
@@ -4632,7 +4653,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>103</v>
       </c>
@@ -4679,7 +4700,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>109</v>
       </c>
@@ -4726,7 +4747,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15.75" customHeight="1">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>115</v>
       </c>
@@ -4773,7 +4794,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15.75" customHeight="1">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>120</v>
       </c>
@@ -4820,7 +4841,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15.75" customHeight="1">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>127</v>
       </c>
@@ -4867,7 +4888,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15.75" customHeight="1">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>132</v>
       </c>
@@ -4914,7 +4935,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15.75" customHeight="1">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>137</v>
       </c>
@@ -4961,7 +4982,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15.75" customHeight="1">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>142</v>
       </c>
@@ -5008,7 +5029,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15.75" customHeight="1">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>147</v>
       </c>
@@ -5055,7 +5076,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15.75" customHeight="1">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>152</v>
       </c>
@@ -5102,7 +5123,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15.75" customHeight="1">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>157</v>
       </c>
@@ -5149,7 +5170,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15.75" customHeight="1">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>162</v>
       </c>
@@ -5196,7 +5217,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15.75" customHeight="1">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>167</v>
       </c>
@@ -5243,7 +5264,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15.75" customHeight="1">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>172</v>
       </c>
@@ -5306,7 +5327,7 @@
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:D36"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="63.33203125" customWidth="1"/>
@@ -5314,7 +5335,7 @@
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="37.5" customHeight="1" thickBot="1">
+    <row r="1" spans="1:4" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="141" t="s">
         <v>368</v>
       </c>
@@ -5322,7 +5343,7 @@
       <c r="C1" s="141"/>
       <c r="D1" s="141"/>
     </row>
-    <row r="2" spans="1:4" ht="30" customHeight="1">
+    <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="142" t="s">
         <v>369</v>
       </c>
@@ -5330,7 +5351,7 @@
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
     </row>
-    <row r="4" spans="1:4" ht="25.5" customHeight="1" thickBot="1">
+    <row r="4" spans="1:4" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="41" t="s">
         <v>370</v>
       </c>
@@ -5338,7 +5359,7 @@
       <c r="C4" s="41"/>
       <c r="D4" s="41"/>
     </row>
-    <row r="5" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="5" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="42" t="s">
         <v>371</v>
       </c>
@@ -5352,7 +5373,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="6" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="42" t="s">
         <v>375</v>
       </c>
@@ -5366,7 +5387,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="7" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="46" t="s">
         <v>377</v>
       </c>
@@ -5380,7 +5401,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="8" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="46" t="s">
         <v>380</v>
       </c>
@@ -5394,7 +5415,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="25.5" customHeight="1" thickBot="1">
+    <row r="9" spans="1:4" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="41" t="s">
         <v>382</v>
       </c>
@@ -5402,7 +5423,7 @@
       <c r="C9" s="41"/>
       <c r="D9" s="41"/>
     </row>
-    <row r="10" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="10" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="42" t="s">
         <v>383</v>
       </c>
@@ -5416,7 +5437,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="11" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="42" t="s">
         <v>385</v>
       </c>
@@ -5430,7 +5451,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="12" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="46" t="s">
         <v>387</v>
       </c>
@@ -5444,7 +5465,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="25.5" customHeight="1" thickBot="1">
+    <row r="13" spans="1:4" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="41" t="s">
         <v>389</v>
       </c>
@@ -5452,7 +5473,7 @@
       <c r="C13" s="41"/>
       <c r="D13" s="41"/>
     </row>
-    <row r="14" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="14" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="42" t="s">
         <v>390</v>
       </c>
@@ -5466,7 +5487,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="15" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="46" t="s">
         <v>392</v>
       </c>
@@ -5480,7 +5501,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="16" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="46" t="s">
         <v>394</v>
       </c>
@@ -5494,7 +5515,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="25.5" customHeight="1" thickBot="1">
+    <row r="17" spans="1:4" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="41" t="s">
         <v>396</v>
       </c>
@@ -5502,7 +5523,7 @@
       <c r="C17" s="41"/>
       <c r="D17" s="41"/>
     </row>
-    <row r="18" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="18" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="42" t="s">
         <v>397</v>
       </c>
@@ -5516,7 +5537,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="19" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="42" t="s">
         <v>399</v>
       </c>
@@ -5530,7 +5551,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="20" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="46" t="s">
         <v>401</v>
       </c>
@@ -5544,7 +5565,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="21" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="46" t="s">
         <v>403</v>
       </c>
@@ -5558,7 +5579,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="25.5" customHeight="1" thickBot="1">
+    <row r="22" spans="1:4" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="41" t="s">
         <v>405</v>
       </c>
@@ -5566,7 +5587,7 @@
       <c r="C22" s="41"/>
       <c r="D22" s="41"/>
     </row>
-    <row r="23" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="23" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="42" t="s">
         <v>406</v>
       </c>
@@ -5580,7 +5601,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="24" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="42" t="s">
         <v>408</v>
       </c>
@@ -5594,7 +5615,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="25" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="42" t="s">
         <v>410</v>
       </c>
@@ -5608,7 +5629,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="25.5" customHeight="1" thickBot="1">
+    <row r="26" spans="1:4" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="41" t="s">
         <v>412</v>
       </c>
@@ -5616,7 +5637,7 @@
       <c r="C26" s="41"/>
       <c r="D26" s="41"/>
     </row>
-    <row r="27" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="27" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="42" t="s">
         <v>413</v>
       </c>
@@ -5630,7 +5651,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="28" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="46" t="s">
         <v>415</v>
       </c>
@@ -5644,7 +5665,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="29" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="42" t="s">
         <v>417</v>
       </c>
@@ -5658,7 +5679,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="25.5" customHeight="1" thickBot="1">
+    <row r="30" spans="1:4" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="41" t="s">
         <v>419</v>
       </c>
@@ -5666,7 +5687,7 @@
       <c r="C30" s="41"/>
       <c r="D30" s="41"/>
     </row>
-    <row r="31" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="31" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="46" t="s">
         <v>420</v>
       </c>
@@ -5680,7 +5701,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="32" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="46" t="s">
         <v>422</v>
       </c>
@@ -5694,7 +5715,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="33" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="42" t="s">
         <v>424</v>
       </c>
@@ -5708,7 +5729,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="25.5" customHeight="1" thickBot="1">
+    <row r="34" spans="1:4" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="41" t="s">
         <v>426</v>
       </c>
@@ -5716,7 +5737,7 @@
       <c r="C34" s="41"/>
       <c r="D34" s="41"/>
     </row>
-    <row r="35" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="35" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="46" t="s">
         <v>427</v>
       </c>
@@ -5730,7 +5751,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="43.5" customHeight="1" thickBot="1">
+    <row r="36" spans="1:4" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="48" t="s">
         <v>429</v>
       </c>
@@ -5760,7 +5781,7 @@
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:F38"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
@@ -5770,7 +5791,7 @@
     <col min="6" max="6" width="51.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="37.5" customHeight="1">
+    <row r="1" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="141" t="s">
         <v>432</v>
       </c>
@@ -5780,7 +5801,7 @@
       <c r="E1" s="141"/>
       <c r="F1" s="141"/>
     </row>
-    <row r="2" spans="1:6" ht="30" customHeight="1">
+    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="142" t="s">
         <v>433</v>
       </c>
@@ -5790,7 +5811,7 @@
       <c r="E2" s="142"/>
       <c r="F2" s="142"/>
     </row>
-    <row r="3" spans="1:6" ht="21.75" customHeight="1">
+    <row r="3" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="50" t="s">
         <v>434</v>
       </c>
@@ -5810,7 +5831,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="31.5" customHeight="1">
+    <row r="4" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="51" t="s">
         <v>440</v>
       </c>
@@ -5830,7 +5851,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="31.5" customHeight="1">
+    <row r="5" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="56" t="s">
         <v>446</v>
       </c>
@@ -5850,7 +5871,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="31.5" customHeight="1">
+    <row r="6" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="51" t="s">
         <v>451</v>
       </c>
@@ -5870,7 +5891,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="31.5" customHeight="1">
+    <row r="7" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="56" t="s">
         <v>180</v>
       </c>
@@ -5890,7 +5911,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="31.5" customHeight="1">
+    <row r="8" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="61" t="s">
         <v>203</v>
       </c>
@@ -5910,7 +5931,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="31.5" customHeight="1">
+    <row r="9" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="66" t="s">
         <v>204</v>
       </c>
@@ -5930,7 +5951,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="31.5" customHeight="1">
+    <row r="10" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="61" t="s">
         <v>205</v>
       </c>
@@ -5950,7 +5971,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="31.5" customHeight="1">
+    <row r="11" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="66" t="s">
         <v>472</v>
       </c>
@@ -5970,7 +5991,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="31.5" customHeight="1">
+    <row r="12" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="61" t="s">
         <v>477</v>
       </c>
@@ -5990,7 +6011,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="31.5" customHeight="1">
+    <row r="13" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="71" t="s">
         <v>482</v>
       </c>
@@ -6010,7 +6031,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="31.5" customHeight="1">
+    <row r="14" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="76" t="s">
         <v>487</v>
       </c>
@@ -6030,7 +6051,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="31.5" customHeight="1">
+    <row r="15" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="71" t="s">
         <v>492</v>
       </c>
@@ -6050,7 +6071,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="31.5" customHeight="1">
+    <row r="16" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="76" t="s">
         <v>497</v>
       </c>
@@ -6070,7 +6091,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="31.5" customHeight="1">
+    <row r="17" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="81" t="s">
         <v>502</v>
       </c>
@@ -6090,7 +6111,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="31.5" customHeight="1">
+    <row r="18" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="86" t="s">
         <v>507</v>
       </c>
@@ -6110,7 +6131,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="31.5" customHeight="1">
+    <row r="19" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="81" t="s">
         <v>512</v>
       </c>
@@ -6130,7 +6151,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="31.5" customHeight="1">
+    <row r="20" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="86" t="s">
         <v>517</v>
       </c>
@@ -6150,7 +6171,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="31.5" customHeight="1">
+    <row r="21" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="91" t="s">
         <v>522</v>
       </c>
@@ -6170,7 +6191,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="31.5" customHeight="1">
+    <row r="22" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="96" t="s">
         <v>527</v>
       </c>
@@ -6190,7 +6211,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="31.5" customHeight="1">
+    <row r="23" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="91" t="s">
         <v>531</v>
       </c>
@@ -6210,7 +6231,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="31.5" customHeight="1">
+    <row r="24" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="96" t="s">
         <v>536</v>
       </c>
@@ -6230,7 +6251,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="31.5" customHeight="1">
+    <row r="25" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="103" t="s">
         <v>299</v>
       </c>
@@ -6250,7 +6271,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="31.5" customHeight="1">
+    <row r="26" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="108" t="s">
         <v>300</v>
       </c>
@@ -6270,7 +6291,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="31.5" customHeight="1">
+    <row r="27" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="103" t="s">
         <v>301</v>
       </c>
@@ -6290,7 +6311,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="31.5" customHeight="1">
+    <row r="28" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="108" t="s">
         <v>553</v>
       </c>
@@ -6310,7 +6331,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="31.5" customHeight="1">
+    <row r="29" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="103" t="s">
         <v>303</v>
       </c>
@@ -6330,7 +6351,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="31.5" customHeight="1">
+    <row r="30" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="113" t="s">
         <v>562</v>
       </c>
@@ -6350,7 +6371,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="31.5" customHeight="1">
+    <row r="31" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="118" t="s">
         <v>567</v>
       </c>
@@ -6370,7 +6391,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="31.5" customHeight="1">
+    <row r="32" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="113" t="s">
         <v>326</v>
       </c>
@@ -6390,7 +6411,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="31.5" customHeight="1">
+    <row r="33" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="118" t="s">
         <v>576</v>
       </c>
@@ -6410,7 +6431,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="31.5" customHeight="1">
+    <row r="34" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="113" t="s">
         <v>581</v>
       </c>
@@ -6430,7 +6451,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="31.5" customHeight="1">
+    <row r="35" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="123" t="s">
         <v>346</v>
       </c>
@@ -6450,7 +6471,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="31.5" customHeight="1">
+    <row r="36" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="128" t="s">
         <v>347</v>
       </c>
@@ -6470,7 +6491,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="31.5" customHeight="1">
+    <row r="37" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="123" t="s">
         <v>348</v>
       </c>
@@ -6490,7 +6511,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="31.5" customHeight="1">
+    <row r="38" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="128" t="s">
         <v>349</v>
       </c>
@@ -6526,7 +6547,7 @@
     <tabColor rgb="FF2E75B6"/>
   </sheetPr>
   <dimension ref="A1:J37"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
     <col min="2" max="2" width="29.109375" customWidth="1"/>
@@ -6537,7 +6558,7 @@
     <col min="9" max="9" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="37.5" customHeight="1" thickBot="1">
+    <row r="1" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="143" t="s">
         <v>177</v>
       </c>
@@ -6548,7 +6569,7 @@
       <c r="F1" s="143"/>
       <c r="G1" s="143"/>
     </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1" thickBot="1">
+    <row r="2" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="142" t="s">
         <v>178</v>
       </c>
@@ -6559,7 +6580,7 @@
       <c r="F2" s="142"/>
       <c r="G2" s="142"/>
     </row>
-    <row r="3" spans="1:10" ht="21.75" customHeight="1" thickBot="1">
+    <row r="3" spans="1:10" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -6582,7 +6603,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1">
+    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -6610,7 +6631,7 @@
         <v>alice.johnson</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.75" customHeight="1">
+    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>28</v>
       </c>
@@ -6638,7 +6659,7 @@
         <v>bob.smith</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+    <row r="6" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
@@ -6666,7 +6687,7 @@
         <v>carol.white</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+    <row r="7" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>45</v>
       </c>
@@ -6700,7 +6721,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+    <row r="8" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>54</v>
       </c>
@@ -6728,7 +6749,7 @@
         <v>eva.green</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
@@ -6762,7 +6783,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+    <row r="10" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>70</v>
       </c>
@@ -6790,7 +6811,7 @@
         <v>grace.kim</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+    <row r="11" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>79</v>
       </c>
@@ -6819,7 +6840,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+    <row r="12" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>85</v>
       </c>
@@ -6842,7 +6863,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+    <row r="13" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>92</v>
       </c>
@@ -6871,29 +6892,47 @@
         <v>602</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+    <row r="14" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>97</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
+      <c r="C14" s="8">
+        <f>LEN(B14)</f>
+        <v>28</v>
+      </c>
+      <c r="D14" s="8" t="str">
+        <f>LEFT(B14,5)</f>
+        <v xml:space="preserve">  kar</v>
+      </c>
+      <c r="E14" s="8" t="str">
+        <f>RIGHT(B14,8)</f>
+        <v xml:space="preserve">il.com  </v>
+      </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+    <row r="15" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>103</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
+      <c r="C15" s="8">
+        <f t="shared" ref="C15:C28" si="0">LEN(B15)</f>
+        <v>22</v>
+      </c>
+      <c r="D15" s="8" t="str">
+        <f t="shared" ref="D15:D28" si="1">LEFT(B15,5)</f>
+        <v xml:space="preserve">  lia</v>
+      </c>
+      <c r="E15" s="8" t="str">
+        <f t="shared" ref="E15:E28" si="2">RIGHT(B15,8)</f>
+        <v xml:space="preserve">orp.in  </v>
+      </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
       <c r="I15" s="1" t="s">
@@ -6903,177 +6942,294 @@
         <v>603</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
+      <c r="C16" s="8">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="D16" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">  mia</v>
+      </c>
+      <c r="E16" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">any.io  </v>
+      </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:10" ht="15.75" customHeight="1">
+    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>115</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
+      <c r="C17" s="8">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D17" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">  noa</v>
+      </c>
+      <c r="E17" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">orp.in  </v>
+      </c>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
       <c r="J17" s="133"/>
     </row>
-    <row r="18" spans="1:10" ht="15.75" customHeight="1">
+    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
+      <c r="C18" s="8">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="D18" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">  oli</v>
+      </c>
+      <c r="E18" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">orp.in  </v>
+      </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:10" ht="15.75" customHeight="1">
+    <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>127</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
+      <c r="C19" s="8">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D19" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">  pet</v>
+      </c>
+      <c r="E19" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">iz.net  </v>
+      </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
     </row>
-    <row r="20" spans="1:10" ht="15.75" customHeight="1">
+    <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
+      <c r="C20" s="8">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="D20" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">  qui</v>
+      </c>
+      <c r="E20" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">il.com  </v>
+      </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:10" ht="15.75" customHeight="1">
+    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>137</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
+      <c r="C21" s="8">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="D21" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">  rya</v>
+      </c>
+      <c r="E21" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">il.com  </v>
+      </c>
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1">
+    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>142</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
+      <c r="C22" s="8">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="D22" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">  sar</v>
+      </c>
+      <c r="E22" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">ok.com  </v>
+      </c>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:10" ht="15.75" customHeight="1">
+    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>147</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
+      <c r="C23" s="8">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="D23" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">  tom</v>
+      </c>
+      <c r="E23" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">ok.com  </v>
+      </c>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
     </row>
-    <row r="24" spans="1:10" ht="15.75" customHeight="1">
+    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>152</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
+      <c r="C24" s="8">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="D24" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">  uma</v>
+      </c>
+      <c r="E24" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">ok.com  </v>
+      </c>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:10" ht="15.75" customHeight="1">
+    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>157</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
+      <c r="C25" s="8">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="D25" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">  vic</v>
+      </c>
+      <c r="E25" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">any.io  </v>
+      </c>
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
     </row>
-    <row r="26" spans="1:10" ht="15.75" customHeight="1">
+    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>162</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
+      <c r="C26" s="8">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="D26" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">  wen</v>
+      </c>
+      <c r="E26" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">ok.com  </v>
+      </c>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:10" ht="15.75" customHeight="1">
+    <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>167</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
+      <c r="C27" s="8">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="D27" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">  xan</v>
+      </c>
+      <c r="E27" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">oo.com  </v>
+      </c>
       <c r="F27" s="11"/>
       <c r="G27" s="11"/>
     </row>
-    <row r="28" spans="1:10" ht="15.75" customHeight="1">
+    <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>172</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
+      <c r="C28" s="8">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D28" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">  yar</v>
+      </c>
+      <c r="E28" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">orp.in  </v>
+      </c>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="30" spans="1:10" ht="25.5" customHeight="1" thickBot="1">
+    <row r="30" spans="1:10" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="144" t="s">
         <v>185</v>
       </c>
@@ -7084,7 +7240,7 @@
       <c r="F30" s="144"/>
       <c r="G30" s="144"/>
     </row>
-    <row r="31" spans="1:10" ht="27.75" customHeight="1" thickBot="1">
+    <row r="31" spans="1:10" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="145" t="s">
         <v>186</v>
       </c>
@@ -7097,7 +7253,7 @@
       <c r="F31" s="146"/>
       <c r="G31" s="146"/>
     </row>
-    <row r="32" spans="1:10" ht="27.75" customHeight="1" thickBot="1">
+    <row r="32" spans="1:10" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="145" t="s">
         <v>188</v>
       </c>
@@ -7110,7 +7266,7 @@
       <c r="F32" s="146"/>
       <c r="G32" s="146"/>
     </row>
-    <row r="33" spans="1:7" ht="27.75" customHeight="1" thickBot="1">
+    <row r="33" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="145" t="s">
         <v>190</v>
       </c>
@@ -7123,7 +7279,7 @@
       <c r="F33" s="146"/>
       <c r="G33" s="146"/>
     </row>
-    <row r="34" spans="1:7" ht="27.75" customHeight="1" thickBot="1">
+    <row r="34" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="145" t="s">
         <v>192</v>
       </c>
@@ -7136,7 +7292,7 @@
       <c r="F34" s="146"/>
       <c r="G34" s="146"/>
     </row>
-    <row r="35" spans="1:7" ht="27.75" customHeight="1" thickBot="1">
+    <row r="35" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="145" t="s">
         <v>194</v>
       </c>
@@ -7149,7 +7305,7 @@
       <c r="F35" s="146"/>
       <c r="G35" s="146"/>
     </row>
-    <row r="36" spans="1:7" ht="27.75" customHeight="1" thickBot="1">
+    <row r="36" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="145" t="s">
         <v>196</v>
       </c>
@@ -7162,7 +7318,7 @@
       <c r="F36" s="146"/>
       <c r="G36" s="146"/>
     </row>
-    <row r="37" spans="1:7" ht="27.75" customHeight="1" thickBot="1">
+    <row r="37" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="145" t="s">
         <v>198</v>
       </c>
@@ -7206,7 +7362,7 @@
     <tabColor rgb="FF1E8449"/>
   </sheetPr>
   <dimension ref="A1:J38"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -7215,7 +7371,7 @@
     <col min="9" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="37.5" customHeight="1" thickBot="1">
+    <row r="1" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="147" t="s">
         <v>200</v>
       </c>
@@ -7226,7 +7382,7 @@
       <c r="F1" s="147"/>
       <c r="G1" s="147"/>
     </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1" thickBot="1">
+    <row r="2" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="148" t="s">
         <v>201</v>
       </c>
@@ -7237,7 +7393,7 @@
       <c r="F2" s="148"/>
       <c r="G2" s="148"/>
     </row>
-    <row r="3" spans="1:10" ht="21.75" customHeight="1" thickBot="1">
+    <row r="3" spans="1:10" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
         <v>2</v>
       </c>
@@ -7260,7 +7416,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1">
+    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -7283,7 +7439,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.75" customHeight="1">
+    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>28</v>
       </c>
@@ -7306,7 +7462,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.75" customHeight="1">
+    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
@@ -7329,7 +7485,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+    <row r="7" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>45</v>
       </c>
@@ -7352,7 +7508,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+    <row r="8" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>54</v>
       </c>
@@ -7371,7 +7527,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
@@ -7384,7 +7540,7 @@
       <c r="F9" s="14"/>
       <c r="G9" s="14"/>
     </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+    <row r="10" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>70</v>
       </c>
@@ -7403,7 +7559,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+    <row r="11" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>79</v>
       </c>
@@ -7416,7 +7572,7 @@
       <c r="F11" s="14"/>
       <c r="G11" s="14"/>
     </row>
-    <row r="12" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+    <row r="12" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>85</v>
       </c>
@@ -7435,7 +7591,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+    <row r="13" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>92</v>
       </c>
@@ -7448,7 +7604,7 @@
       <c r="F13" s="14"/>
       <c r="G13" s="14"/>
     </row>
-    <row r="14" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+    <row r="14" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>97</v>
       </c>
@@ -7467,7 +7623,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+    <row r="15" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>103</v>
       </c>
@@ -7480,7 +7636,7 @@
       <c r="F15" s="14"/>
       <c r="G15" s="14"/>
     </row>
-    <row r="16" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+    <row r="16" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>109</v>
       </c>
@@ -7499,7 +7655,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1">
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>115</v>
       </c>
@@ -7512,7 +7668,7 @@
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
     </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1">
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>120</v>
       </c>
@@ -7525,7 +7681,7 @@
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1">
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>127</v>
       </c>
@@ -7538,7 +7694,7 @@
       <c r="F19" s="14"/>
       <c r="G19" s="14"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1">
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>132</v>
       </c>
@@ -7551,7 +7707,7 @@
       <c r="F20" s="13"/>
       <c r="G20" s="13"/>
     </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1">
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>137</v>
       </c>
@@ -7564,7 +7720,7 @@
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
     </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1">
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>142</v>
       </c>
@@ -7577,7 +7733,7 @@
       <c r="F22" s="13"/>
       <c r="G22" s="13"/>
     </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1">
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>147</v>
       </c>
@@ -7590,7 +7746,7 @@
       <c r="F23" s="14"/>
       <c r="G23" s="14"/>
     </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1">
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>152</v>
       </c>
@@ -7603,7 +7759,7 @@
       <c r="F24" s="13"/>
       <c r="G24" s="13"/>
     </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1">
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>157</v>
       </c>
@@ -7616,7 +7772,7 @@
       <c r="F25" s="14"/>
       <c r="G25" s="14"/>
     </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1">
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>162</v>
       </c>
@@ -7629,7 +7785,7 @@
       <c r="F26" s="13"/>
       <c r="G26" s="13"/>
     </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1">
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>167</v>
       </c>
@@ -7642,7 +7798,7 @@
       <c r="F27" s="14"/>
       <c r="G27" s="14"/>
     </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1">
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>172</v>
       </c>
@@ -7655,7 +7811,7 @@
       <c r="F28" s="13"/>
       <c r="G28" s="13"/>
     </row>
-    <row r="30" spans="1:7" ht="25.5" customHeight="1" thickBot="1">
+    <row r="30" spans="1:7" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="149" t="s">
         <v>185</v>
       </c>
@@ -7666,7 +7822,7 @@
       <c r="F30" s="149"/>
       <c r="G30" s="149"/>
     </row>
-    <row r="31" spans="1:7" ht="27.75" customHeight="1" thickBot="1">
+    <row r="31" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="150" t="s">
         <v>208</v>
       </c>
@@ -7679,7 +7835,7 @@
       <c r="F31" s="146"/>
       <c r="G31" s="146"/>
     </row>
-    <row r="32" spans="1:7" ht="27.75" customHeight="1" thickBot="1">
+    <row r="32" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="150" t="s">
         <v>210</v>
       </c>
@@ -7692,7 +7848,7 @@
       <c r="F32" s="146"/>
       <c r="G32" s="146"/>
     </row>
-    <row r="33" spans="1:7" ht="27.75" customHeight="1" thickBot="1">
+    <row r="33" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="150" t="s">
         <v>212</v>
       </c>
@@ -7705,7 +7861,7 @@
       <c r="F33" s="146"/>
       <c r="G33" s="146"/>
     </row>
-    <row r="34" spans="1:7" ht="27.75" customHeight="1" thickBot="1">
+    <row r="34" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="150" t="s">
         <v>214</v>
       </c>
@@ -7718,7 +7874,7 @@
       <c r="F34" s="146"/>
       <c r="G34" s="146"/>
     </row>
-    <row r="35" spans="1:7" ht="27.75" customHeight="1" thickBot="1">
+    <row r="35" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="150" t="s">
         <v>216</v>
       </c>
@@ -7731,7 +7887,7 @@
       <c r="F35" s="146"/>
       <c r="G35" s="146"/>
     </row>
-    <row r="36" spans="1:7" ht="27.75" customHeight="1" thickBot="1">
+    <row r="36" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="150" t="s">
         <v>218</v>
       </c>
@@ -7744,7 +7900,7 @@
       <c r="F36" s="146"/>
       <c r="G36" s="146"/>
     </row>
-    <row r="37" spans="1:7" ht="27.75" customHeight="1" thickBot="1">
+    <row r="37" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="150" t="s">
         <v>220</v>
       </c>
@@ -7757,7 +7913,7 @@
       <c r="F37" s="146"/>
       <c r="G37" s="146"/>
     </row>
-    <row r="38" spans="1:7" ht="27.75" customHeight="1" thickBot="1">
+    <row r="38" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="150" t="s">
         <v>222</v>
       </c>
@@ -7803,7 +7959,7 @@
     <tabColor rgb="FFB7560A"/>
   </sheetPr>
   <dimension ref="A1:O38"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -7816,7 +7972,7 @@
     <col min="10" max="10" width="24.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="37.5" customHeight="1">
+    <row r="1" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="151" t="s">
         <v>224</v>
       </c>
@@ -7828,7 +7984,7 @@
       <c r="G1" s="151"/>
       <c r="H1" s="151"/>
     </row>
-    <row r="2" spans="1:11" ht="30" customHeight="1">
+    <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="152" t="s">
         <v>225</v>
       </c>
@@ -7840,7 +7996,7 @@
       <c r="G2" s="152"/>
       <c r="H2" s="152"/>
     </row>
-    <row r="3" spans="1:11" ht="21.75" customHeight="1">
+    <row r="3" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>2</v>
       </c>
@@ -7866,7 +8022,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.75" customHeight="1">
+    <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -7892,7 +8048,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.75" customHeight="1">
+    <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>28</v>
       </c>
@@ -7918,7 +8074,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
+    <row r="6" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
@@ -7944,7 +8100,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
+    <row r="7" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>45</v>
       </c>
@@ -7976,7 +8132,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.75" customHeight="1">
+    <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>54</v>
       </c>
@@ -7995,7 +8151,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
+    <row r="9" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
@@ -8011,7 +8167,7 @@
       <c r="G9" s="19"/>
       <c r="H9" s="18"/>
     </row>
-    <row r="10" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
+    <row r="10" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>70</v>
       </c>
@@ -8033,7 +8189,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15.75" customHeight="1">
+    <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>79</v>
       </c>
@@ -8052,7 +8208,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
+    <row r="12" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>85</v>
       </c>
@@ -8068,7 +8224,7 @@
       <c r="G12" s="17"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
+    <row r="13" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>92</v>
       </c>
@@ -8090,7 +8246,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15.75" customHeight="1">
+    <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>97</v>
       </c>
@@ -8109,7 +8265,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
+    <row r="15" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>103</v>
       </c>
@@ -8125,7 +8281,7 @@
       <c r="G15" s="19"/>
       <c r="H15" s="18"/>
     </row>
-    <row r="16" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
+    <row r="16" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>109</v>
       </c>
@@ -8147,7 +8303,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15.75" customHeight="1">
+    <row r="17" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>115</v>
       </c>
@@ -8166,7 +8322,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15.75" customHeight="1">
+    <row r="18" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>120</v>
       </c>
@@ -8185,7 +8341,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15.75" customHeight="1">
+    <row r="19" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>127</v>
       </c>
@@ -8201,7 +8357,7 @@
       <c r="G19" s="19"/>
       <c r="H19" s="18"/>
     </row>
-    <row r="20" spans="1:15" ht="15.75" customHeight="1" thickBot="1">
+    <row r="20" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>132</v>
       </c>
@@ -8217,7 +8373,7 @@
       <c r="G20" s="17"/>
       <c r="H20" s="16"/>
     </row>
-    <row r="21" spans="1:15" ht="15.75" customHeight="1" thickBot="1">
+    <row r="21" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>137</v>
       </c>
@@ -8239,7 +8395,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15.75" customHeight="1">
+    <row r="22" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>142</v>
       </c>
@@ -8270,7 +8426,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15.75" customHeight="1">
+    <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>147</v>
       </c>
@@ -8289,7 +8445,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15.75" customHeight="1">
+    <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>152</v>
       </c>
@@ -8305,7 +8461,7 @@
       <c r="G24" s="17"/>
       <c r="H24" s="16"/>
     </row>
-    <row r="25" spans="1:15" ht="15.75" customHeight="1">
+    <row r="25" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>157</v>
       </c>
@@ -8321,7 +8477,7 @@
       <c r="G25" s="19"/>
       <c r="H25" s="18"/>
     </row>
-    <row r="26" spans="1:15" ht="15.75" customHeight="1">
+    <row r="26" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>162</v>
       </c>
@@ -8338,7 +8494,7 @@
       <c r="H26" s="16"/>
       <c r="K26" s="136"/>
     </row>
-    <row r="27" spans="1:15" ht="15.75" customHeight="1">
+    <row r="27" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>167</v>
       </c>
@@ -8354,7 +8510,7 @@
       <c r="G27" s="19"/>
       <c r="H27" s="18"/>
     </row>
-    <row r="28" spans="1:15" ht="15.75" customHeight="1">
+    <row r="28" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>172</v>
       </c>
@@ -8371,8 +8527,8 @@
       <c r="H28" s="16"/>
       <c r="K28" s="136"/>
     </row>
-    <row r="29" spans="1:15" ht="15" thickBot="1"/>
-    <row r="30" spans="1:15" ht="25.5" customHeight="1" thickBot="1">
+    <row r="29" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="1:15" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="153" t="s">
         <v>185</v>
       </c>
@@ -8385,7 +8541,7 @@
       <c r="H30" s="153"/>
       <c r="K30" s="136"/>
     </row>
-    <row r="31" spans="1:15" ht="27.75" customHeight="1" thickBot="1">
+    <row r="31" spans="1:15" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="154" t="s">
         <v>232</v>
       </c>
@@ -8398,7 +8554,7 @@
       <c r="F31" s="146"/>
       <c r="G31" s="146"/>
     </row>
-    <row r="32" spans="1:15" ht="27.75" customHeight="1" thickBot="1">
+    <row r="32" spans="1:15" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="154" t="s">
         <v>234</v>
       </c>
@@ -8411,7 +8567,7 @@
       <c r="F32" s="146"/>
       <c r="G32" s="146"/>
     </row>
-    <row r="33" spans="1:7" ht="27.75" customHeight="1" thickBot="1">
+    <row r="33" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="154" t="s">
         <v>236</v>
       </c>
@@ -8424,7 +8580,7 @@
       <c r="F33" s="146"/>
       <c r="G33" s="146"/>
     </row>
-    <row r="34" spans="1:7" ht="27.75" customHeight="1" thickBot="1">
+    <row r="34" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="154" t="s">
         <v>238</v>
       </c>
@@ -8437,7 +8593,7 @@
       <c r="F34" s="146"/>
       <c r="G34" s="146"/>
     </row>
-    <row r="35" spans="1:7" ht="27.75" customHeight="1">
+    <row r="35" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="154" t="s">
         <v>240</v>
       </c>
@@ -8450,7 +8606,7 @@
       <c r="F35" s="146"/>
       <c r="G35" s="146"/>
     </row>
-    <row r="36" spans="1:7" ht="27.75" customHeight="1">
+    <row r="36" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="154" t="s">
         <v>242</v>
       </c>
@@ -8463,7 +8619,7 @@
       <c r="F36" s="146"/>
       <c r="G36" s="146"/>
     </row>
-    <row r="37" spans="1:7" ht="27.75" customHeight="1">
+    <row r="37" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="154" t="s">
         <v>244</v>
       </c>
@@ -8476,7 +8632,7 @@
       <c r="F37" s="146"/>
       <c r="G37" s="146"/>
     </row>
-    <row r="38" spans="1:7" ht="27.75" customHeight="1">
+    <row r="38" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="154" t="s">
         <v>246</v>
       </c>
@@ -8522,7 +8678,7 @@
     <tabColor rgb="FF6C3483"/>
   </sheetPr>
   <dimension ref="A1:H49"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="3" width="20" customWidth="1"/>
@@ -8534,7 +8690,7 @@
     <col min="10" max="10" width="20.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="37.5" customHeight="1">
+    <row r="1" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="155" t="s">
         <v>248</v>
       </c>
@@ -8546,7 +8702,7 @@
       <c r="G1" s="155"/>
       <c r="H1" s="155"/>
     </row>
-    <row r="2" spans="1:8" ht="30" customHeight="1">
+    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="156" t="s">
         <v>249</v>
       </c>
@@ -8558,7 +8714,7 @@
       <c r="G2" s="156"/>
       <c r="H2" s="156"/>
     </row>
-    <row r="3" spans="1:8" ht="21.75" customHeight="1">
+    <row r="3" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -8584,7 +8740,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -8610,7 +8766,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>28</v>
       </c>
@@ -8636,7 +8792,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
@@ -8662,7 +8818,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>45</v>
       </c>
@@ -8688,7 +8844,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>54</v>
       </c>
@@ -8714,7 +8870,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
@@ -8726,7 +8882,7 @@
       <c r="G9" s="21"/>
       <c r="H9" s="21"/>
     </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1">
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>70</v>
       </c>
@@ -8738,7 +8894,7 @@
       <c r="G10" s="21"/>
       <c r="H10" s="21"/>
     </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>79</v>
       </c>
@@ -8750,7 +8906,7 @@
       <c r="G11" s="22"/>
       <c r="H11" s="22"/>
     </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1">
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>85</v>
       </c>
@@ -8762,7 +8918,7 @@
       <c r="G12" s="21"/>
       <c r="H12" s="21"/>
     </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1">
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>92</v>
       </c>
@@ -8774,7 +8930,7 @@
       <c r="G13" s="22"/>
       <c r="H13" s="22"/>
     </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1">
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>97</v>
       </c>
@@ -8786,7 +8942,7 @@
       <c r="G14" s="21"/>
       <c r="H14" s="21"/>
     </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1">
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>103</v>
       </c>
@@ -8798,7 +8954,7 @@
       <c r="G15" s="22"/>
       <c r="H15" s="22"/>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1">
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>109</v>
       </c>
@@ -8810,7 +8966,7 @@
       <c r="G16" s="21"/>
       <c r="H16" s="21"/>
     </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1">
+    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>115</v>
       </c>
@@ -8822,7 +8978,7 @@
       <c r="G17" s="22"/>
       <c r="H17" s="22"/>
     </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1">
+    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>120</v>
       </c>
@@ -8834,7 +8990,7 @@
       <c r="G18" s="21"/>
       <c r="H18" s="21"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
+    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>127</v>
       </c>
@@ -8846,7 +9002,7 @@
       <c r="G19" s="22"/>
       <c r="H19" s="22"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1">
+    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>132</v>
       </c>
@@ -8858,7 +9014,7 @@
       <c r="G20" s="21"/>
       <c r="H20" s="21"/>
     </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1">
+    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>137</v>
       </c>
@@ -8870,7 +9026,7 @@
       <c r="G21" s="22"/>
       <c r="H21" s="22"/>
     </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1">
+    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>142</v>
       </c>
@@ -8882,7 +9038,7 @@
       <c r="G22" s="21"/>
       <c r="H22" s="21"/>
     </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1">
+    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>147</v>
       </c>
@@ -8894,7 +9050,7 @@
       <c r="G23" s="22"/>
       <c r="H23" s="22"/>
     </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1">
+    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>152</v>
       </c>
@@ -8906,7 +9062,7 @@
       <c r="G24" s="21"/>
       <c r="H24" s="21"/>
     </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1">
+    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>157</v>
       </c>
@@ -8918,7 +9074,7 @@
       <c r="G25" s="22"/>
       <c r="H25" s="22"/>
     </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1">
+    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>162</v>
       </c>
@@ -8930,7 +9086,7 @@
       <c r="G26" s="21"/>
       <c r="H26" s="21"/>
     </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1">
+    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>167</v>
       </c>
@@ -8942,7 +9098,7 @@
       <c r="G27" s="22"/>
       <c r="H27" s="22"/>
     </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1">
+    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>172</v>
       </c>
@@ -8954,7 +9110,7 @@
       <c r="G28" s="21"/>
       <c r="H28" s="21"/>
     </row>
-    <row r="30" spans="1:8" ht="25.5" customHeight="1">
+    <row r="30" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="157" t="s">
         <v>185</v>
       </c>
@@ -8966,7 +9122,7 @@
       <c r="G30" s="157"/>
       <c r="H30" s="157"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" customHeight="1">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="158" t="s">
         <v>257</v>
       </c>
@@ -8979,7 +9135,7 @@
       <c r="F31" s="146"/>
       <c r="G31" s="146"/>
     </row>
-    <row r="32" spans="1:8" ht="27.75" customHeight="1">
+    <row r="32" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="158" t="s">
         <v>259</v>
       </c>
@@ -8992,7 +9148,7 @@
       <c r="F32" s="146"/>
       <c r="G32" s="146"/>
     </row>
-    <row r="33" spans="1:7" ht="27.75" customHeight="1">
+    <row r="33" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="158" t="s">
         <v>261</v>
       </c>
@@ -9005,7 +9161,7 @@
       <c r="F33" s="146"/>
       <c r="G33" s="146"/>
     </row>
-    <row r="34" spans="1:7" ht="27.75" customHeight="1">
+    <row r="34" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="158" t="s">
         <v>263</v>
       </c>
@@ -9018,7 +9174,7 @@
       <c r="F34" s="146"/>
       <c r="G34" s="146"/>
     </row>
-    <row r="35" spans="1:7" ht="27.75" customHeight="1">
+    <row r="35" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="158" t="s">
         <v>265</v>
       </c>
@@ -9031,7 +9187,7 @@
       <c r="F35" s="146"/>
       <c r="G35" s="146"/>
     </row>
-    <row r="36" spans="1:7" ht="27.75" customHeight="1">
+    <row r="36" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="158" t="s">
         <v>267</v>
       </c>
@@ -9044,7 +9200,7 @@
       <c r="F36" s="146"/>
       <c r="G36" s="146"/>
     </row>
-    <row r="37" spans="1:7" ht="27.75" customHeight="1">
+    <row r="37" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="158" t="s">
         <v>269</v>
       </c>
@@ -9057,7 +9213,7 @@
       <c r="F37" s="146"/>
       <c r="G37" s="146"/>
     </row>
-    <row r="38" spans="1:7" ht="27.75" customHeight="1">
+    <row r="38" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="158" t="s">
         <v>271</v>
       </c>
@@ -9070,7 +9226,7 @@
       <c r="F38" s="146"/>
       <c r="G38" s="146"/>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>626</v>
       </c>
@@ -9093,7 +9249,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>632</v>
       </c>
@@ -9116,7 +9272,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>638</v>
       </c>
@@ -9139,7 +9295,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>645</v>
       </c>
@@ -9162,7 +9318,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>651</v>
       </c>
@@ -9218,7 +9374,7 @@
     <tabColor rgb="FF0E6655"/>
   </sheetPr>
   <dimension ref="A1:L38"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -9230,7 +9386,7 @@
     <col min="11" max="11" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="37.5" customHeight="1">
+    <row r="1" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="159" t="s">
         <v>273</v>
       </c>
@@ -9242,7 +9398,7 @@
       <c r="G1" s="159"/>
       <c r="H1" s="159"/>
     </row>
-    <row r="2" spans="1:12" ht="30" customHeight="1">
+    <row r="2" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="160" t="s">
         <v>274</v>
       </c>
@@ -9254,7 +9410,7 @@
       <c r="G2" s="160"/>
       <c r="H2" s="160"/>
     </row>
-    <row r="3" spans="1:12" ht="21.75" customHeight="1">
+    <row r="3" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -9280,7 +9436,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15.75" customHeight="1">
+    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -9306,7 +9462,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.75" customHeight="1">
+    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>28</v>
       </c>
@@ -9332,7 +9488,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
+    <row r="6" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
@@ -9358,7 +9514,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
+    <row r="7" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>45</v>
       </c>
@@ -9390,7 +9546,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>54</v>
       </c>
@@ -9416,7 +9572,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
+    <row r="9" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
@@ -9448,7 +9604,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15.75" customHeight="1">
+    <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>70</v>
       </c>
@@ -9477,7 +9633,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15.75" customHeight="1">
+    <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>79</v>
       </c>
@@ -9506,7 +9662,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75" customHeight="1">
+    <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>85</v>
       </c>
@@ -9523,7 +9679,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15.75" customHeight="1">
+    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>92</v>
       </c>
@@ -9537,7 +9693,7 @@
       <c r="G13" s="29"/>
       <c r="H13" s="29"/>
     </row>
-    <row r="14" spans="1:12" ht="15.75" customHeight="1">
+    <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>97</v>
       </c>
@@ -9552,7 +9708,7 @@
       <c r="H14" s="25"/>
       <c r="L14" s="136"/>
     </row>
-    <row r="15" spans="1:12" ht="15.75" customHeight="1">
+    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>103</v>
       </c>
@@ -9566,7 +9722,7 @@
       <c r="G15" s="29"/>
       <c r="H15" s="29"/>
     </row>
-    <row r="16" spans="1:12" ht="15.75" customHeight="1">
+    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>109</v>
       </c>
@@ -9580,7 +9736,7 @@
       <c r="G16" s="25"/>
       <c r="H16" s="25"/>
     </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1">
+    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>115</v>
       </c>
@@ -9594,7 +9750,7 @@
       <c r="G17" s="29"/>
       <c r="H17" s="29"/>
     </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1">
+    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>120</v>
       </c>
@@ -9608,7 +9764,7 @@
       <c r="G18" s="25"/>
       <c r="H18" s="25"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
+    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>127</v>
       </c>
@@ -9622,7 +9778,7 @@
       <c r="G19" s="29"/>
       <c r="H19" s="29"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1">
+    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>132</v>
       </c>
@@ -9636,7 +9792,7 @@
       <c r="G20" s="25"/>
       <c r="H20" s="25"/>
     </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1">
+    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>137</v>
       </c>
@@ -9650,7 +9806,7 @@
       <c r="G21" s="29"/>
       <c r="H21" s="29"/>
     </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1">
+    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>142</v>
       </c>
@@ -9664,7 +9820,7 @@
       <c r="G22" s="25"/>
       <c r="H22" s="25"/>
     </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1">
+    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>147</v>
       </c>
@@ -9678,7 +9834,7 @@
       <c r="G23" s="29"/>
       <c r="H23" s="29"/>
     </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1">
+    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>152</v>
       </c>
@@ -9692,7 +9848,7 @@
       <c r="G24" s="25"/>
       <c r="H24" s="25"/>
     </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1">
+    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>157</v>
       </c>
@@ -9706,7 +9862,7 @@
       <c r="G25" s="29"/>
       <c r="H25" s="29"/>
     </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1">
+    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>162</v>
       </c>
@@ -9720,7 +9876,7 @@
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
     </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1">
+    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>167</v>
       </c>
@@ -9734,7 +9890,7 @@
       <c r="G27" s="29"/>
       <c r="H27" s="29"/>
     </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1">
+    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>172</v>
       </c>
@@ -9748,7 +9904,7 @@
       <c r="G28" s="25"/>
       <c r="H28" s="25"/>
     </row>
-    <row r="30" spans="1:8" ht="25.5" customHeight="1">
+    <row r="30" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="161" t="s">
         <v>185</v>
       </c>
@@ -9760,7 +9916,7 @@
       <c r="G30" s="161"/>
       <c r="H30" s="161"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" customHeight="1">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="162" t="s">
         <v>281</v>
       </c>
@@ -9773,7 +9929,7 @@
       <c r="F31" s="146"/>
       <c r="G31" s="146"/>
     </row>
-    <row r="32" spans="1:8" ht="27.75" customHeight="1">
+    <row r="32" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="162" t="s">
         <v>283</v>
       </c>
@@ -9786,7 +9942,7 @@
       <c r="F32" s="146"/>
       <c r="G32" s="146"/>
     </row>
-    <row r="33" spans="1:7" ht="27.75" customHeight="1">
+    <row r="33" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="162" t="s">
         <v>285</v>
       </c>
@@ -9799,7 +9955,7 @@
       <c r="F33" s="146"/>
       <c r="G33" s="146"/>
     </row>
-    <row r="34" spans="1:7" ht="27.75" customHeight="1">
+    <row r="34" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="162" t="s">
         <v>287</v>
       </c>
@@ -9812,7 +9968,7 @@
       <c r="F34" s="146"/>
       <c r="G34" s="146"/>
     </row>
-    <row r="35" spans="1:7" ht="27.75" customHeight="1">
+    <row r="35" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="162" t="s">
         <v>289</v>
       </c>
@@ -9825,7 +9981,7 @@
       <c r="F35" s="146"/>
       <c r="G35" s="146"/>
     </row>
-    <row r="36" spans="1:7" ht="27.75" customHeight="1">
+    <row r="36" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="162" t="s">
         <v>291</v>
       </c>
@@ -9838,7 +9994,7 @@
       <c r="F36" s="146"/>
       <c r="G36" s="146"/>
     </row>
-    <row r="37" spans="1:7" ht="27.75" customHeight="1">
+    <row r="37" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="162" t="s">
         <v>293</v>
       </c>
@@ -9851,7 +10007,7 @@
       <c r="F37" s="146"/>
       <c r="G37" s="146"/>
     </row>
-    <row r="38" spans="1:7" ht="27.75" customHeight="1">
+    <row r="38" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="162" t="s">
         <v>295</v>
       </c>
@@ -9897,7 +10053,7 @@
     <tabColor rgb="FF283593"/>
   </sheetPr>
   <dimension ref="A1:H38"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -9907,7 +10063,7 @@
     <col min="8" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="37.5" customHeight="1">
+    <row r="1" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="163" t="s">
         <v>297</v>
       </c>
@@ -9919,7 +10075,7 @@
       <c r="G1" s="163"/>
       <c r="H1" s="163"/>
     </row>
-    <row r="2" spans="1:8" ht="30" customHeight="1">
+    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="164" t="s">
         <v>298</v>
       </c>
@@ -9931,7 +10087,7 @@
       <c r="G2" s="164"/>
       <c r="H2" s="164"/>
     </row>
-    <row r="3" spans="1:8" ht="21.75" customHeight="1">
+    <row r="3" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="32" t="s">
         <v>2</v>
       </c>
@@ -9957,7 +10113,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -9983,7 +10139,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>28</v>
       </c>
@@ -10009,7 +10165,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
@@ -10035,7 +10191,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>45</v>
       </c>
@@ -10061,7 +10217,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>54</v>
       </c>
@@ -10075,7 +10231,7 @@
       <c r="G8" s="33"/>
       <c r="H8" s="33"/>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
@@ -10089,7 +10245,7 @@
       <c r="G9" s="34"/>
       <c r="H9" s="34"/>
     </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1">
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>70</v>
       </c>
@@ -10103,7 +10259,7 @@
       <c r="G10" s="33"/>
       <c r="H10" s="33"/>
     </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>79</v>
       </c>
@@ -10117,7 +10273,7 @@
       <c r="G11" s="34"/>
       <c r="H11" s="34"/>
     </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1">
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>85</v>
       </c>
@@ -10131,7 +10287,7 @@
       <c r="G12" s="33"/>
       <c r="H12" s="33"/>
     </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1">
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>92</v>
       </c>
@@ -10145,7 +10301,7 @@
       <c r="G13" s="34"/>
       <c r="H13" s="34"/>
     </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1">
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>97</v>
       </c>
@@ -10159,7 +10315,7 @@
       <c r="G14" s="33"/>
       <c r="H14" s="33"/>
     </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1">
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>103</v>
       </c>
@@ -10173,7 +10329,7 @@
       <c r="G15" s="34"/>
       <c r="H15" s="34"/>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1">
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>109</v>
       </c>
@@ -10187,7 +10343,7 @@
       <c r="G16" s="33"/>
       <c r="H16" s="33"/>
     </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1">
+    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>115</v>
       </c>
@@ -10201,7 +10357,7 @@
       <c r="G17" s="34"/>
       <c r="H17" s="34"/>
     </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1">
+    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>120</v>
       </c>
@@ -10215,7 +10371,7 @@
       <c r="G18" s="33"/>
       <c r="H18" s="33"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
+    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>127</v>
       </c>
@@ -10229,7 +10385,7 @@
       <c r="G19" s="34"/>
       <c r="H19" s="34"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1">
+    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>132</v>
       </c>
@@ -10243,7 +10399,7 @@
       <c r="G20" s="33"/>
       <c r="H20" s="33"/>
     </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1">
+    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>137</v>
       </c>
@@ -10257,7 +10413,7 @@
       <c r="G21" s="34"/>
       <c r="H21" s="34"/>
     </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1">
+    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>142</v>
       </c>
@@ -10271,7 +10427,7 @@
       <c r="G22" s="33"/>
       <c r="H22" s="33"/>
     </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1">
+    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>147</v>
       </c>
@@ -10285,7 +10441,7 @@
       <c r="G23" s="34"/>
       <c r="H23" s="34"/>
     </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1">
+    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>152</v>
       </c>
@@ -10299,7 +10455,7 @@
       <c r="G24" s="33"/>
       <c r="H24" s="33"/>
     </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1">
+    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>157</v>
       </c>
@@ -10313,7 +10469,7 @@
       <c r="G25" s="34"/>
       <c r="H25" s="34"/>
     </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1">
+    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>162</v>
       </c>
@@ -10327,7 +10483,7 @@
       <c r="G26" s="33"/>
       <c r="H26" s="33"/>
     </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1">
+    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>167</v>
       </c>
@@ -10341,7 +10497,7 @@
       <c r="G27" s="34"/>
       <c r="H27" s="34"/>
     </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1">
+    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>172</v>
       </c>
@@ -10355,7 +10511,7 @@
       <c r="G28" s="33"/>
       <c r="H28" s="33"/>
     </row>
-    <row r="30" spans="1:8" ht="25.5" customHeight="1">
+    <row r="30" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="165" t="s">
         <v>185</v>
       </c>
@@ -10367,7 +10523,7 @@
       <c r="G30" s="165"/>
       <c r="H30" s="165"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" customHeight="1">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="166" t="s">
         <v>305</v>
       </c>
@@ -10380,7 +10536,7 @@
       <c r="F31" s="146"/>
       <c r="G31" s="146"/>
     </row>
-    <row r="32" spans="1:8" ht="27.75" customHeight="1">
+    <row r="32" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="166" t="s">
         <v>307</v>
       </c>
@@ -10393,7 +10549,7 @@
       <c r="F32" s="146"/>
       <c r="G32" s="146"/>
     </row>
-    <row r="33" spans="1:7" ht="27.75" customHeight="1">
+    <row r="33" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="166" t="s">
         <v>309</v>
       </c>
@@ -10406,7 +10562,7 @@
       <c r="F33" s="146"/>
       <c r="G33" s="146"/>
     </row>
-    <row r="34" spans="1:7" ht="27.75" customHeight="1">
+    <row r="34" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="166" t="s">
         <v>311</v>
       </c>
@@ -10419,7 +10575,7 @@
       <c r="F34" s="146"/>
       <c r="G34" s="146"/>
     </row>
-    <row r="35" spans="1:7" ht="27.75" customHeight="1">
+    <row r="35" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="166" t="s">
         <v>313</v>
       </c>
@@ -10432,7 +10588,7 @@
       <c r="F35" s="146"/>
       <c r="G35" s="146"/>
     </row>
-    <row r="36" spans="1:7" ht="27.75" customHeight="1">
+    <row r="36" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="166" t="s">
         <v>315</v>
       </c>
@@ -10445,7 +10601,7 @@
       <c r="F36" s="146"/>
       <c r="G36" s="146"/>
     </row>
-    <row r="37" spans="1:7" ht="27.75" customHeight="1">
+    <row r="37" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="166" t="s">
         <v>317</v>
       </c>
@@ -10458,7 +10614,7 @@
       <c r="F37" s="146"/>
       <c r="G37" s="146"/>
     </row>
-    <row r="38" spans="1:7" ht="27.75" customHeight="1">
+    <row r="38" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="166" t="s">
         <v>319</v>
       </c>
@@ -10504,7 +10660,7 @@
     <tabColor rgb="FF6E2F1A"/>
   </sheetPr>
   <dimension ref="A1:H38"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="3" width="13" customWidth="1"/>
@@ -10514,7 +10670,7 @@
     <col min="8" max="8" width="24.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="37.5" customHeight="1">
+    <row r="1" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="167" t="s">
         <v>321</v>
       </c>
@@ -10526,7 +10682,7 @@
       <c r="G1" s="167"/>
       <c r="H1" s="167"/>
     </row>
-    <row r="2" spans="1:8" ht="30" customHeight="1">
+    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="168" t="s">
         <v>322</v>
       </c>
@@ -10538,7 +10694,7 @@
       <c r="G2" s="168"/>
       <c r="H2" s="168"/>
     </row>
-    <row r="3" spans="1:8" ht="21.75" customHeight="1">
+    <row r="3" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="35" t="s">
         <v>2</v>
       </c>
@@ -10564,7 +10720,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -10590,7 +10746,7 @@
         <v>44542</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>28</v>
       </c>
@@ -10616,7 +10772,7 @@
         <v>44985</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
@@ -10642,7 +10798,7 @@
         <v>44836</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>45</v>
       </c>
@@ -10668,7 +10824,7 @@
         <v>44470</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>54</v>
       </c>
@@ -10694,7 +10850,7 @@
         <v>44624</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
@@ -10710,7 +10866,7 @@
       <c r="G9" s="37"/>
       <c r="H9" s="139"/>
     </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1">
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>70</v>
       </c>
@@ -10726,7 +10882,7 @@
       <c r="G10" s="36"/>
       <c r="H10" s="138"/>
     </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>79</v>
       </c>
@@ -10742,7 +10898,7 @@
       <c r="G11" s="37"/>
       <c r="H11" s="139"/>
     </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1">
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>85</v>
       </c>
@@ -10758,7 +10914,7 @@
       <c r="G12" s="36"/>
       <c r="H12" s="138"/>
     </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1">
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>92</v>
       </c>
@@ -10774,7 +10930,7 @@
       <c r="G13" s="37"/>
       <c r="H13" s="139"/>
     </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1">
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>97</v>
       </c>
@@ -10790,7 +10946,7 @@
       <c r="G14" s="36"/>
       <c r="H14" s="138"/>
     </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1">
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>103</v>
       </c>
@@ -10806,7 +10962,7 @@
       <c r="G15" s="37"/>
       <c r="H15" s="139"/>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1">
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>109</v>
       </c>
@@ -10822,7 +10978,7 @@
       <c r="G16" s="36"/>
       <c r="H16" s="138"/>
     </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1">
+    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>115</v>
       </c>
@@ -10838,7 +10994,7 @@
       <c r="G17" s="37"/>
       <c r="H17" s="139"/>
     </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1">
+    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>120</v>
       </c>
@@ -10854,7 +11010,7 @@
       <c r="G18" s="36"/>
       <c r="H18" s="138"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
+    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>127</v>
       </c>
@@ -10870,7 +11026,7 @@
       <c r="G19" s="37"/>
       <c r="H19" s="139"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1">
+    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>132</v>
       </c>
@@ -10886,7 +11042,7 @@
       <c r="G20" s="36"/>
       <c r="H20" s="138"/>
     </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1">
+    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>137</v>
       </c>
@@ -10902,7 +11058,7 @@
       <c r="G21" s="37"/>
       <c r="H21" s="139"/>
     </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1">
+    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>142</v>
       </c>
@@ -10918,7 +11074,7 @@
       <c r="G22" s="36"/>
       <c r="H22" s="138"/>
     </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1">
+    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>147</v>
       </c>
@@ -10934,7 +11090,7 @@
       <c r="G23" s="37"/>
       <c r="H23" s="139"/>
     </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1">
+    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>152</v>
       </c>
@@ -10950,7 +11106,7 @@
       <c r="G24" s="36"/>
       <c r="H24" s="138"/>
     </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1">
+    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>157</v>
       </c>
@@ -10966,7 +11122,7 @@
       <c r="G25" s="37"/>
       <c r="H25" s="139"/>
     </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1">
+    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>162</v>
       </c>
@@ -10982,7 +11138,7 @@
       <c r="G26" s="36"/>
       <c r="H26" s="138"/>
     </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1">
+    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>167</v>
       </c>
@@ -10998,7 +11154,7 @@
       <c r="G27" s="37"/>
       <c r="H27" s="139"/>
     </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1">
+    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>172</v>
       </c>
@@ -11014,7 +11170,7 @@
       <c r="G28" s="36"/>
       <c r="H28" s="138"/>
     </row>
-    <row r="30" spans="1:8" ht="25.5" customHeight="1">
+    <row r="30" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="169" t="s">
         <v>185</v>
       </c>
@@ -11026,7 +11182,7 @@
       <c r="G30" s="169"/>
       <c r="H30" s="169"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" customHeight="1">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="170" t="s">
         <v>327</v>
       </c>
@@ -11039,7 +11195,7 @@
       <c r="F31" s="146"/>
       <c r="G31" s="146"/>
     </row>
-    <row r="32" spans="1:8" ht="27.75" customHeight="1">
+    <row r="32" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="170" t="s">
         <v>329</v>
       </c>
@@ -11052,7 +11208,7 @@
       <c r="F32" s="146"/>
       <c r="G32" s="146"/>
     </row>
-    <row r="33" spans="1:7" ht="27.75" customHeight="1">
+    <row r="33" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="170" t="s">
         <v>331</v>
       </c>
@@ -11065,7 +11221,7 @@
       <c r="F33" s="146"/>
       <c r="G33" s="146"/>
     </row>
-    <row r="34" spans="1:7" ht="27.75" customHeight="1">
+    <row r="34" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="170" t="s">
         <v>333</v>
       </c>
@@ -11078,7 +11234,7 @@
       <c r="F34" s="146"/>
       <c r="G34" s="146"/>
     </row>
-    <row r="35" spans="1:7" ht="27.75" customHeight="1">
+    <row r="35" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="170" t="s">
         <v>335</v>
       </c>
@@ -11091,7 +11247,7 @@
       <c r="F35" s="146"/>
       <c r="G35" s="146"/>
     </row>
-    <row r="36" spans="1:7" ht="27.75" customHeight="1">
+    <row r="36" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="170" t="s">
         <v>337</v>
       </c>
@@ -11104,7 +11260,7 @@
       <c r="F36" s="146"/>
       <c r="G36" s="146"/>
     </row>
-    <row r="37" spans="1:7" ht="27.75" customHeight="1">
+    <row r="37" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="170" t="s">
         <v>339</v>
       </c>
@@ -11117,7 +11273,7 @@
       <c r="F37" s="146"/>
       <c r="G37" s="146"/>
     </row>
-    <row r="38" spans="1:7" ht="27.75" customHeight="1">
+    <row r="38" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="170" t="s">
         <v>341</v>
       </c>
@@ -11163,7 +11319,7 @@
     <tabColor rgb="FF6B0F1A"/>
   </sheetPr>
   <dimension ref="A1:L38"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -11174,7 +11330,7 @@
     <col min="11" max="11" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="37.5" customHeight="1">
+    <row r="1" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="171" t="s">
         <v>343</v>
       </c>
@@ -11186,7 +11342,7 @@
       <c r="G1" s="171"/>
       <c r="H1" s="171"/>
     </row>
-    <row r="2" spans="1:12" ht="30" customHeight="1">
+    <row r="2" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="172" t="s">
         <v>344</v>
       </c>
@@ -11198,7 +11354,7 @@
       <c r="G2" s="172"/>
       <c r="H2" s="172"/>
     </row>
-    <row r="3" spans="1:12" ht="21.75" customHeight="1">
+    <row r="3" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="38" t="s">
         <v>2</v>
       </c>
@@ -11224,7 +11380,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15.75" customHeight="1">
+    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -11250,7 +11406,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.75" customHeight="1">
+    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>28</v>
       </c>
@@ -11276,7 +11432,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.75" customHeight="1">
+    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
@@ -11302,7 +11458,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
+    <row r="7" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>45</v>
       </c>
@@ -11328,7 +11484,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>54</v>
       </c>
@@ -11360,7 +11516,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15.75" customHeight="1">
+    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
@@ -11374,7 +11530,7 @@
       <c r="G9" s="40"/>
       <c r="H9" s="40"/>
     </row>
-    <row r="10" spans="1:12" ht="15.75" customHeight="1">
+    <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>70</v>
       </c>
@@ -11388,7 +11544,7 @@
       <c r="G10" s="39"/>
       <c r="H10" s="39"/>
     </row>
-    <row r="11" spans="1:12" ht="15.75" customHeight="1">
+    <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>79</v>
       </c>
@@ -11402,7 +11558,7 @@
       <c r="G11" s="40"/>
       <c r="H11" s="40"/>
     </row>
-    <row r="12" spans="1:12" ht="15.75" customHeight="1">
+    <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>85</v>
       </c>
@@ -11416,7 +11572,7 @@
       <c r="G12" s="39"/>
       <c r="H12" s="39"/>
     </row>
-    <row r="13" spans="1:12" ht="15.75" customHeight="1">
+    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>92</v>
       </c>
@@ -11430,7 +11586,7 @@
       <c r="G13" s="40"/>
       <c r="H13" s="40"/>
     </row>
-    <row r="14" spans="1:12" ht="15.75" customHeight="1">
+    <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>97</v>
       </c>
@@ -11444,7 +11600,7 @@
       <c r="G14" s="39"/>
       <c r="H14" s="39"/>
     </row>
-    <row r="15" spans="1:12" ht="15.75" customHeight="1">
+    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>103</v>
       </c>
@@ -11458,7 +11614,7 @@
       <c r="G15" s="40"/>
       <c r="H15" s="40"/>
     </row>
-    <row r="16" spans="1:12" ht="15.75" customHeight="1">
+    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>109</v>
       </c>
@@ -11472,7 +11628,7 @@
       <c r="G16" s="39"/>
       <c r="H16" s="39"/>
     </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1">
+    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>115</v>
       </c>
@@ -11486,7 +11642,7 @@
       <c r="G17" s="40"/>
       <c r="H17" s="40"/>
     </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1">
+    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>120</v>
       </c>
@@ -11500,7 +11656,7 @@
       <c r="G18" s="39"/>
       <c r="H18" s="39"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
+    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>127</v>
       </c>
@@ -11514,7 +11670,7 @@
       <c r="G19" s="40"/>
       <c r="H19" s="40"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1">
+    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>132</v>
       </c>
@@ -11528,7 +11684,7 @@
       <c r="G20" s="39"/>
       <c r="H20" s="39"/>
     </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1">
+    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>137</v>
       </c>
@@ -11542,7 +11698,7 @@
       <c r="G21" s="40"/>
       <c r="H21" s="40"/>
     </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1">
+    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>142</v>
       </c>
@@ -11556,7 +11712,7 @@
       <c r="G22" s="39"/>
       <c r="H22" s="39"/>
     </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1">
+    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>147</v>
       </c>
@@ -11570,7 +11726,7 @@
       <c r="G23" s="40"/>
       <c r="H23" s="40"/>
     </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1">
+    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>152</v>
       </c>
@@ -11584,7 +11740,7 @@
       <c r="G24" s="39"/>
       <c r="H24" s="39"/>
     </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1">
+    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>157</v>
       </c>
@@ -11598,7 +11754,7 @@
       <c r="G25" s="40"/>
       <c r="H25" s="40"/>
     </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1">
+    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>162</v>
       </c>
@@ -11612,7 +11768,7 @@
       <c r="G26" s="39"/>
       <c r="H26" s="39"/>
     </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1">
+    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>167</v>
       </c>
@@ -11626,7 +11782,7 @@
       <c r="G27" s="40"/>
       <c r="H27" s="40"/>
     </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1">
+    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>172</v>
       </c>
@@ -11640,7 +11796,7 @@
       <c r="G28" s="39"/>
       <c r="H28" s="39"/>
     </row>
-    <row r="30" spans="1:8" ht="25.5" customHeight="1">
+    <row r="30" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="173" t="s">
         <v>185</v>
       </c>
@@ -11652,7 +11808,7 @@
       <c r="G30" s="173"/>
       <c r="H30" s="173"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" customHeight="1">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="174" t="s">
         <v>352</v>
       </c>
@@ -11665,7 +11821,7 @@
       <c r="F31" s="146"/>
       <c r="G31" s="146"/>
     </row>
-    <row r="32" spans="1:8" ht="27.75" customHeight="1">
+    <row r="32" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="174" t="s">
         <v>354</v>
       </c>
@@ -11678,7 +11834,7 @@
       <c r="F32" s="146"/>
       <c r="G32" s="146"/>
     </row>
-    <row r="33" spans="1:7" ht="27.75" customHeight="1">
+    <row r="33" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="174" t="s">
         <v>356</v>
       </c>
@@ -11691,7 +11847,7 @@
       <c r="F33" s="146"/>
       <c r="G33" s="146"/>
     </row>
-    <row r="34" spans="1:7" ht="27.75" customHeight="1">
+    <row r="34" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="174" t="s">
         <v>358</v>
       </c>
@@ -11704,7 +11860,7 @@
       <c r="F34" s="146"/>
       <c r="G34" s="146"/>
     </row>
-    <row r="35" spans="1:7" ht="27.75" customHeight="1">
+    <row r="35" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="174" t="s">
         <v>360</v>
       </c>
@@ -11717,7 +11873,7 @@
       <c r="F35" s="146"/>
       <c r="G35" s="146"/>
     </row>
-    <row r="36" spans="1:7" ht="27.75" customHeight="1">
+    <row r="36" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="174" t="s">
         <v>362</v>
       </c>
@@ -11730,7 +11886,7 @@
       <c r="F36" s="146"/>
       <c r="G36" s="146"/>
     </row>
-    <row r="37" spans="1:7" ht="27.75" customHeight="1">
+    <row r="37" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="174" t="s">
         <v>364</v>
       </c>
@@ -11743,7 +11899,7 @@
       <c r="F37" s="146"/>
       <c r="G37" s="146"/>
     </row>
-    <row r="38" spans="1:7" ht="27.75" customHeight="1">
+    <row r="38" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="174" t="s">
         <v>366</v>
       </c>
